--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0002.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0002.xlsx
@@ -2016,7 +2016,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Ingen religion alls</t>
+          <t>Reformert kristendom</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Helt nya ryska lagar</t>
+          <t>Ryska lagar och förordningar</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>EU-parlamentet</t>
+          <t>Senaten</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Kommunfullmäktige</t>
+          <t>Statsrådet</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Hovrätten</t>
+          <t>Riksdagen</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Rymdfart</t>
+          <t>Sjöfart</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Tropiskt jordbruk</t>
+          <t>Utbildningsväsendet</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Vulkanforskning</t>
+          <t>Skogsindustrin</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Inga fabriker fanns</t>
+          <t>Industrialiseringen gick långsammare</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Massproduktion förbjöds</t>
+          <t>Industrialiseringen var begränsad till jordbruk</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Avskaffande av städer</t>
+          <t>Mekanisering av jordbruket</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Total nedstängning av handel</t>
+          <t>Utbyggnad av järnvägar</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot maskiner</t>
+          <t>Fackföreningar växte fram</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Snö och is</t>
+          <t>Maskiner och energi</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Guld och silver</t>
+          <t>Kapital och teknik</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Fisk och salt</t>
+          <t>Transporter och marknader</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>För att undvika skola</t>
+          <t>För att få bättre bostäder</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>För att slippa skatt</t>
+          <t>För att komma närmare skolor och service</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>För att bli präster</t>
+          <t>För att slippa arbeta på gården</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Från 10 till 100 miljoner</t>
+          <t>Från ca 0,5 miljon till ca 2 miljoner</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Från 5 miljoner till 50 miljoner</t>
+          <t>Från ca 2 miljoner till ca 4 miljoner</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Den minskade kraftigt</t>
+          <t>Den låg kvar runt ca 1 miljon</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Den försvann helt</t>
+          <t>Den minskade under flera perioder</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Den halverades</t>
+          <t>Den stagnerade</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Den förbjöds</t>
+          <t>Den blev mer beroende av import</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Den räckte aldrig i någon del</t>
+          <t>Den räckte i regel för hela landet</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Den blev gratis för alla</t>
+          <t>Den räckte främst i städerna</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Den kunde bara exporteras</t>
+          <t>Den räckte främst på landsbygden</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Bilindustrin</t>
+          <t>Textilindustrin</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Flygindustrin</t>
+          <t>Metallindustrin</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Oljeindustrin</t>
+          <t>Varvsindustrin</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Kaffe och kakao</t>
+          <t>Metallprodukter</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Olja</t>
+          <t>Textilier</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Siden</t>
+          <t>Livsmedel</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
